--- a/data/trans_orig/P34B03-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P34B03-Estudios-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de días a la semana que la población realiza una actividad física moderada, como montar en bicicleta, gimnasia, aeróbic,correr, natación</t>
+          <t>Número medio de días a la semana que, durante más de 30 minutos, la población realiza una actividad física moderada, como montar en bicicleta, gimnasia, aeróbic,correr, natación (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,33</t>
+          <t>0,19; 0,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,2</t>
+          <t>0,12; 0,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -702,12 +702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,17</t>
+          <t>0,07; 0,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,23</t>
+          <t>0,16; 0,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -792,17 +792,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 0,99</t>
+          <t>0,83; 0,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,01</t>
+          <t>0,58; 1,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,4</t>
+          <t>0,29; 0,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,41</t>
+          <t>0,26; 0,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,67</t>
+          <t>0,57; 0,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,69</t>
+          <t>0,49; 0,7</t>
         </is>
       </c>
     </row>
@@ -897,37 +897,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,51</t>
+          <t>1,13; 1,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,44</t>
+          <t>1,1; 1,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,23</t>
+          <t>0,91; 1,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,84</t>
+          <t>0,55; 0,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,02</t>
+          <t>0,73; 1,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 0,96</t>
+          <t>0,74; 0,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,14</t>
+          <t>0,88; 1,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 0,81</t>
+          <t>0,7; 0,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1017,37 +1017,37 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,91</t>
+          <t>0,64; 0,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,36</t>
+          <t>0,28; 0,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,52</t>
+          <t>0,43; 0,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,44</t>
+          <t>0,31; 0,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,57</t>
+          <t>0,5; 0,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,7</t>
+          <t>0,63; 0,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 0,65</t>
+          <t>0,51; 0,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P34B03-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P34B03-Estudios-trans_orig.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 0,56</t>
+          <t>0,36; 0,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -697,12 +697,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,23</t>
+          <t>0,12; 0,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,17</t>
+          <t>0,08; 0,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,22</t>
+          <t>0,13; 0,21</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,4</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,67</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 0,99</t>
+          <t>0,84; 0,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,0</t>
+          <t>0,85; 1,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,4</t>
+          <t>0,3; 0,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,58</t>
+          <t>0,46; 0,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,41</t>
+          <t>0,35; 0,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,68</t>
+          <t>0,57; 0,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,7</t>
+          <t>0,62; 0,73</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>0,94</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 1,53</t>
+          <t>1,12; 1,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,45</t>
+          <t>1,1; 1,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,21</t>
+          <t>0,91; 1,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,83</t>
+          <t>0,54; 0,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,0</t>
+          <t>0,73; 1,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 0,97</t>
+          <t>0,71; 0,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,12</t>
+          <t>0,87; 1,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,19</t>
+          <t>0,95; 1,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,05</t>
+          <t>0,85; 1,03</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,63</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 0,93</t>
+          <t>0,8; 0,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 0,91</t>
+          <t>0,79; 0,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1027,27 +1027,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,51</t>
+          <t>0,43; 0,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,43</t>
+          <t>0,38; 0,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,57</t>
+          <t>0,49; 0,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,71</t>
+          <t>0,63; 0,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,64</t>
+          <t>0,59; 0,67</t>
         </is>
       </c>
     </row>
